--- a/app/src/main/assets/rutina_plantilla.xlsx
+++ b/app/src/main/assets/rutina_plantilla.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" r:id="R7c81ff1577ed4f3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semana 1" sheetId="2" r:id="Rb7314a5b54e74a39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semana 2" sheetId="3" r:id="R6d206d809db943ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semana 3" sheetId="4" r:id="R4cf93d8cf5ce4e00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semana 4" sheetId="5" r:id="R5e93d5d7b8d94534"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternativas" sheetId="6" r:id="Rd6c4509a1a5649fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recuperación" sheetId="7" r:id="R4d4ca74fc82845e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mañana" sheetId="8" r:id="Re03ab3ff450f4d0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" r:id="R6913c1a71bd04315"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semana 1" sheetId="2" r:id="R9f39d669c8704698"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semana 2" sheetId="3" r:id="R1424244d745c4d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semana 3" sheetId="4" r:id="Refed0f42383c49ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semana 4" sheetId="5" r:id="R514bf89593264205"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternativas" sheetId="6" r:id="R2649db11f05d4db0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recuperación" sheetId="7" r:id="R72c58bb6db084eca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mañana" sheetId="8" r:id="Rbe5f497bba7f4e6c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="17">
+  <x:fonts count="20">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -120,8 +120,25 @@
       <x:color rgb="FF147A52"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF172033"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF172033"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="30">
+  <x:fills count="32">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -268,6 +285,16 @@
         <x:fgColor rgb="FFEAF5EE"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3263FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFB8323B"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="4">
     <x:border/>
@@ -291,7 +318,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="117">
+  <x:cellXfs count="125">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -577,6 +604,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="16" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1204,11 +1243,86 @@
       <x:c r="I20" s="32"/>
       <x:c r="J20" s="32"/>
     </x:row>
+    <x:row r="21" ht="26" customHeight="1">
+      <x:c r="A21" s="124" t="str">
+        <x:v>Vídeos de ejercicios</x:v>
+      </x:c>
+      <x:c r="B21" s="123"/>
+      <x:c r="C21" s="123"/>
+      <x:c r="D21" s="123"/>
+      <x:c r="E21" s="123"/>
+      <x:c r="F21" s="123"/>
+      <x:c r="G21" s="123"/>
+      <x:c r="H21" s="123"/>
+      <x:c r="I21" s="123"/>
+      <x:c r="J21" s="123"/>
+    </x:row>
+    <x:row r="22" ht="26" customHeight="1">
+      <x:c r="A22" s="123" t="str">
+        <x:v>Pega la URL completa de YouTube en Vídeo: L en las semanas, E en Mañana y G en Recuperación.</x:v>
+      </x:c>
+      <x:c r="B22" s="123"/>
+      <x:c r="C22" s="123"/>
+      <x:c r="D22" s="123"/>
+      <x:c r="E22" s="123"/>
+      <x:c r="F22" s="123"/>
+      <x:c r="G22" s="123"/>
+      <x:c r="H22" s="123"/>
+      <x:c r="I22" s="123"/>
+      <x:c r="J22" s="123"/>
+    </x:row>
+    <x:row r="23" ht="26" customHeight="1">
+      <x:c r="A23" s="123" t="str">
+        <x:v>Ejemplo incluido: Sentadillas sin peso. Puedes sustituir el enlace o dejar la celda vacía.</x:v>
+      </x:c>
+      <x:c r="B23" s="123"/>
+      <x:c r="C23" s="123"/>
+      <x:c r="D23" s="123"/>
+      <x:c r="E23" s="123"/>
+      <x:c r="F23" s="123"/>
+      <x:c r="G23" s="123"/>
+      <x:c r="H23" s="123"/>
+      <x:c r="I23" s="123"/>
+      <x:c r="J23" s="123"/>
+    </x:row>
+    <x:row r="24" ht="26" customHeight="1">
+      <x:c r="A24" s="123" t="str">
+        <x:v>No cambies el orden de las columnas. Usa la URL como texto, no una fórmula HIPERVINCULO.</x:v>
+      </x:c>
+      <x:c r="B24" s="123"/>
+      <x:c r="C24" s="123"/>
+      <x:c r="D24" s="123"/>
+      <x:c r="E24" s="123"/>
+      <x:c r="F24" s="123"/>
+      <x:c r="G24" s="123"/>
+      <x:c r="H24" s="123"/>
+      <x:c r="I24" s="123"/>
+      <x:c r="J24" s="123"/>
+    </x:row>
+    <x:row r="25" ht="26" customHeight="1">
+      <x:c r="A25" s="123" t="str">
+        <x:v>La reproducción requiere Internet; si el vídeo está restringido, pulsa Abrir en YouTube en la app.</x:v>
+      </x:c>
+      <x:c r="B25" s="123"/>
+      <x:c r="C25" s="123"/>
+      <x:c r="D25" s="123"/>
+      <x:c r="E25" s="123"/>
+      <x:c r="F25" s="123"/>
+      <x:c r="G25" s="123"/>
+      <x:c r="H25" s="123"/>
+      <x:c r="I25" s="123"/>
+      <x:c r="J25" s="123"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J2"/>
     <x:mergeCell ref="A19:J20"/>
     <x:mergeCell ref="A19:J19"/>
+    <x:mergeCell ref="A21:J21"/>
+    <x:mergeCell ref="A22:J22"/>
+    <x:mergeCell ref="A23:J23"/>
+    <x:mergeCell ref="A24:J24"/>
+    <x:mergeCell ref="A25:J25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1228,6 +1342,8 @@
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="48" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -1313,6 +1429,12 @@
       <x:c r="J5" s="62" t="str">
         <x:v>Hecho</x:v>
       </x:c>
+      <x:c r="K5" s="119" t="str">
+        <x:v>Indicaciones</x:v>
+      </x:c>
+      <x:c r="L5" s="119" t="str">
+        <x:v>Vídeo (YouTube, opcional)</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="73" t="str">
@@ -1339,6 +1461,8 @@
       <x:c r="J6" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="73" t="str">
@@ -1365,6 +1489,10 @@
       <x:c r="J7" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K7"/>
+      <x:c r="L7" t="str">
+        <x:v>https://www.youtube.com/watch?v=50KX3DZxw60</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="73" t="str">
@@ -1391,6 +1519,8 @@
       <x:c r="J8" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="73" t="str">
@@ -1417,6 +1547,8 @@
       <x:c r="J9" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="73" t="str">
@@ -1443,6 +1575,8 @@
       <x:c r="J10" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="73" t="str">
@@ -1469,6 +1603,8 @@
       <x:c r="J11" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="73" t="str">
@@ -1495,6 +1631,8 @@
       <x:c r="J12" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="73" t="str">
@@ -1521,6 +1659,8 @@
       <x:c r="J13" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="73" t="str">
@@ -1547,6 +1687,8 @@
       <x:c r="J14" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="73" t="str">
@@ -1573,6 +1715,8 @@
       <x:c r="J15" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="73" t="str">
@@ -1599,6 +1743,8 @@
       <x:c r="J16" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="74" t="str">
@@ -1625,6 +1771,8 @@
       <x:c r="J17" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="74" t="str">
@@ -1651,6 +1799,8 @@
       <x:c r="J18" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="74" t="str">
@@ -1677,6 +1827,8 @@
       <x:c r="J19" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="74" t="str">
@@ -1703,6 +1855,8 @@
       <x:c r="J20" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="76" t="str">
@@ -1729,6 +1883,8 @@
       <x:c r="J21" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="76" t="str">
@@ -1755,6 +1911,8 @@
       <x:c r="J22" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="76" t="str">
@@ -1781,6 +1939,8 @@
       <x:c r="J23" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K23"/>
+      <x:c r="L23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="76" t="str">
@@ -1807,6 +1967,8 @@
       <x:c r="J24" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K24"/>
+      <x:c r="L24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="76" t="str">
@@ -1833,6 +1995,8 @@
       <x:c r="J25" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K25"/>
+      <x:c r="L25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="76" t="str">
@@ -1859,6 +2023,8 @@
       <x:c r="J26" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K26"/>
+      <x:c r="L26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="76" t="str">
@@ -1885,6 +2051,8 @@
       <x:c r="J27" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K27"/>
+      <x:c r="L27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="76" t="str">
@@ -1911,6 +2079,8 @@
       <x:c r="J28" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K28"/>
+      <x:c r="L28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="76" t="str">
@@ -1937,6 +2107,8 @@
       <x:c r="J29" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="76" t="str">
@@ -1963,6 +2135,8 @@
       <x:c r="J30" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K30"/>
+      <x:c r="L30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="76" t="str">
@@ -1989,6 +2163,8 @@
       <x:c r="J31" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K31"/>
+      <x:c r="L31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="74" t="str">
@@ -2015,6 +2191,8 @@
       <x:c r="J32" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="74" t="str">
@@ -2041,6 +2219,8 @@
       <x:c r="J33" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K33"/>
+      <x:c r="L33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="74" t="str">
@@ -2067,6 +2247,8 @@
       <x:c r="J34" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K34"/>
+      <x:c r="L34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="74" t="str">
@@ -2093,6 +2275,8 @@
       <x:c r="J35" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K35"/>
+      <x:c r="L35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="77" t="str">
@@ -2119,6 +2303,8 @@
       <x:c r="J36" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K36"/>
+      <x:c r="L36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="77" t="str">
@@ -2145,6 +2331,8 @@
       <x:c r="J37" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K37"/>
+      <x:c r="L37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="77" t="str">
@@ -2171,6 +2359,8 @@
       <x:c r="J38" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K38"/>
+      <x:c r="L38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="77" t="str">
@@ -2197,6 +2387,8 @@
       <x:c r="J39" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K39"/>
+      <x:c r="L39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="77" t="str">
@@ -2223,6 +2415,8 @@
       <x:c r="J40" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K40"/>
+      <x:c r="L40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="77" t="str">
@@ -2249,6 +2443,8 @@
       <x:c r="J41" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K41"/>
+      <x:c r="L41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="74" t="str">
@@ -2275,6 +2471,8 @@
       <x:c r="J42" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K42"/>
+      <x:c r="L42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="74" t="str">
@@ -2301,6 +2499,8 @@
       <x:c r="J43" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K43"/>
+      <x:c r="L43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="74" t="str">
@@ -2327,6 +2527,8 @@
       <x:c r="J44" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K44"/>
+      <x:c r="L44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="74"/>
@@ -2339,6 +2541,8 @@
       <x:c r="H45" s="74"/>
       <x:c r="I45" s="74"/>
       <x:c r="J45" s="74"/>
+      <x:c r="K45"/>
+      <x:c r="L45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="78" t="str">
@@ -2365,6 +2569,8 @@
       <x:c r="J46" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K46"/>
+      <x:c r="L46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="78" t="str">
@@ -2391,6 +2597,10 @@
       <x:c r="J47" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K47"/>
+      <x:c r="L47" t="str">
+        <x:v>https://www.youtube.com/watch?v=50KX3DZxw60</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="78" t="str">
@@ -2417,6 +2627,8 @@
       <x:c r="J48" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K48"/>
+      <x:c r="L48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="78" t="str">
@@ -2443,6 +2655,8 @@
       <x:c r="J49" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K49"/>
+      <x:c r="L49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="78" t="str">
@@ -2469,6 +2683,8 @@
       <x:c r="J50" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K50"/>
+      <x:c r="L50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="78" t="str">
@@ -2495,6 +2711,8 @@
       <x:c r="J51" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K51"/>
+      <x:c r="L51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="78" t="str">
@@ -2521,6 +2739,8 @@
       <x:c r="J52" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K52"/>
+      <x:c r="L52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="78" t="str">
@@ -2547,6 +2767,8 @@
       <x:c r="J53" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K53"/>
+      <x:c r="L53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="78" t="str">
@@ -2573,6 +2795,8 @@
       <x:c r="J54" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K54"/>
+      <x:c r="L54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="78" t="str">
@@ -2599,6 +2823,8 @@
       <x:c r="J55" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K55"/>
+      <x:c r="L55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="78" t="str">
@@ -2625,6 +2851,8 @@
       <x:c r="J56" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K56"/>
+      <x:c r="L56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="74" t="str">
@@ -2651,6 +2879,8 @@
       <x:c r="J57" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K57"/>
+      <x:c r="L57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="74" t="str">
@@ -2677,6 +2907,8 @@
       <x:c r="J58" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K58"/>
+      <x:c r="L58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="74" t="str">
@@ -2703,6 +2935,8 @@
       <x:c r="J59" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K59"/>
+      <x:c r="L59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="74" t="str">
@@ -2729,6 +2963,8 @@
       <x:c r="J60" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K60"/>
+      <x:c r="L60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="79" t="str">
@@ -2755,6 +2991,8 @@
       <x:c r="J61" s="79" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K61"/>
+      <x:c r="L61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="79"/>
@@ -2767,6 +3005,8 @@
       <x:c r="H62" s="79"/>
       <x:c r="I62" s="79"/>
       <x:c r="J62" s="79"/>
+      <x:c r="K62"/>
+      <x:c r="L62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="80" t="str">
@@ -2793,6 +3033,8 @@
       <x:c r="J63" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K63"/>
+      <x:c r="L63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="80" t="str">
@@ -2819,6 +3061,8 @@
       <x:c r="J64" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K64"/>
+      <x:c r="L64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="80" t="str">
@@ -2845,6 +3089,8 @@
       <x:c r="J65" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K65"/>
+      <x:c r="L65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="80" t="str">
@@ -2871,6 +3117,8 @@
       <x:c r="J66" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K66"/>
+      <x:c r="L66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="80" t="str">
@@ -2897,6 +3145,8 @@
       <x:c r="J67" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K67"/>
+      <x:c r="L67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="80" t="str">
@@ -2923,6 +3173,8 @@
       <x:c r="J68" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K68"/>
+      <x:c r="L68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="80" t="str">
@@ -2949,6 +3201,8 @@
       <x:c r="J69" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K69"/>
+      <x:c r="L69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="80" t="str">
@@ -2975,6 +3229,8 @@
       <x:c r="J70" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K70"/>
+      <x:c r="L70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="80" t="str">
@@ -3001,6 +3257,8 @@
       <x:c r="J71" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K71"/>
+      <x:c r="L71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="80" t="str">
@@ -3027,6 +3285,8 @@
       <x:c r="J72" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K72"/>
+      <x:c r="L72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="74" t="str">
@@ -3053,6 +3313,8 @@
       <x:c r="J73" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K73"/>
+      <x:c r="L73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="74" t="str">
@@ -3079,6 +3341,8 @@
       <x:c r="J74" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K74"/>
+      <x:c r="L74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="74" t="str">
@@ -3105,6 +3369,8 @@
       <x:c r="J75" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K75"/>
+      <x:c r="L75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="74" t="str">
@@ -3131,6 +3397,8 @@
       <x:c r="J76" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K76"/>
+      <x:c r="L76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="74" t="str">
@@ -3157,6 +3425,8 @@
       <x:c r="J77" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K77"/>
+      <x:c r="L77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="81" t="str">
@@ -3183,6 +3453,8 @@
       <x:c r="J78" s="81" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K78"/>
+      <x:c r="L78"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3226,6 +3498,8 @@
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="48" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -3311,6 +3585,12 @@
       <x:c r="J5" s="62" t="str">
         <x:v>Hecho</x:v>
       </x:c>
+      <x:c r="K5" s="119" t="str">
+        <x:v>Indicaciones</x:v>
+      </x:c>
+      <x:c r="L5" s="119" t="str">
+        <x:v>Vídeo (YouTube, opcional)</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="73" t="str">
@@ -3337,6 +3617,8 @@
       <x:c r="J6" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="73" t="str">
@@ -3363,6 +3645,10 @@
       <x:c r="J7" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K7"/>
+      <x:c r="L7" t="str">
+        <x:v>https://www.youtube.com/watch?v=50KX3DZxw60</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="73" t="str">
@@ -3389,6 +3675,8 @@
       <x:c r="J8" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="73" t="str">
@@ -3415,6 +3703,8 @@
       <x:c r="J9" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="73" t="str">
@@ -3441,6 +3731,8 @@
       <x:c r="J10" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="73" t="str">
@@ -3467,6 +3759,8 @@
       <x:c r="J11" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="73" t="str">
@@ -3493,6 +3787,8 @@
       <x:c r="J12" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="73" t="str">
@@ -3519,6 +3815,8 @@
       <x:c r="J13" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="73" t="str">
@@ -3545,6 +3843,8 @@
       <x:c r="J14" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="73" t="str">
@@ -3571,6 +3871,8 @@
       <x:c r="J15" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="73" t="str">
@@ -3597,6 +3899,8 @@
       <x:c r="J16" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="74" t="str">
@@ -3623,6 +3927,8 @@
       <x:c r="J17" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="74" t="str">
@@ -3649,6 +3955,8 @@
       <x:c r="J18" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="74" t="str">
@@ -3675,6 +3983,8 @@
       <x:c r="J19" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="74" t="str">
@@ -3701,6 +4011,8 @@
       <x:c r="J20" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="76" t="str">
@@ -3727,6 +4039,8 @@
       <x:c r="J21" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="76" t="str">
@@ -3753,6 +4067,8 @@
       <x:c r="J22" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="76" t="str">
@@ -3779,6 +4095,8 @@
       <x:c r="J23" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K23"/>
+      <x:c r="L23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="76" t="str">
@@ -3805,6 +4123,8 @@
       <x:c r="J24" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K24"/>
+      <x:c r="L24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="76" t="str">
@@ -3831,6 +4151,8 @@
       <x:c r="J25" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K25"/>
+      <x:c r="L25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="76" t="str">
@@ -3857,6 +4179,8 @@
       <x:c r="J26" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K26"/>
+      <x:c r="L26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="76" t="str">
@@ -3883,6 +4207,8 @@
       <x:c r="J27" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K27"/>
+      <x:c r="L27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="76" t="str">
@@ -3909,6 +4235,8 @@
       <x:c r="J28" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K28"/>
+      <x:c r="L28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="76" t="str">
@@ -3935,6 +4263,8 @@
       <x:c r="J29" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="76" t="str">
@@ -3961,6 +4291,8 @@
       <x:c r="J30" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K30"/>
+      <x:c r="L30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="76" t="str">
@@ -3987,6 +4319,8 @@
       <x:c r="J31" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K31"/>
+      <x:c r="L31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="74" t="str">
@@ -4013,6 +4347,8 @@
       <x:c r="J32" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="74" t="str">
@@ -4039,6 +4375,8 @@
       <x:c r="J33" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K33"/>
+      <x:c r="L33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="74" t="str">
@@ -4065,6 +4403,8 @@
       <x:c r="J34" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K34"/>
+      <x:c r="L34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="74" t="str">
@@ -4091,6 +4431,8 @@
       <x:c r="J35" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K35"/>
+      <x:c r="L35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="77" t="str">
@@ -4117,6 +4459,8 @@
       <x:c r="J36" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K36"/>
+      <x:c r="L36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="77" t="str">
@@ -4143,6 +4487,8 @@
       <x:c r="J37" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K37"/>
+      <x:c r="L37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="77" t="str">
@@ -4169,6 +4515,8 @@
       <x:c r="J38" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K38"/>
+      <x:c r="L38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="77" t="str">
@@ -4195,6 +4543,8 @@
       <x:c r="J39" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K39"/>
+      <x:c r="L39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="77" t="str">
@@ -4221,6 +4571,8 @@
       <x:c r="J40" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K40"/>
+      <x:c r="L40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="77" t="str">
@@ -4247,6 +4599,8 @@
       <x:c r="J41" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K41"/>
+      <x:c r="L41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="74" t="str">
@@ -4273,6 +4627,8 @@
       <x:c r="J42" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K42"/>
+      <x:c r="L42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="74" t="str">
@@ -4299,6 +4655,8 @@
       <x:c r="J43" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K43"/>
+      <x:c r="L43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="74" t="str">
@@ -4325,6 +4683,8 @@
       <x:c r="J44" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K44"/>
+      <x:c r="L44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="74"/>
@@ -4337,6 +4697,8 @@
       <x:c r="H45" s="74"/>
       <x:c r="I45" s="74"/>
       <x:c r="J45" s="74"/>
+      <x:c r="K45"/>
+      <x:c r="L45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="78" t="str">
@@ -4363,6 +4725,8 @@
       <x:c r="J46" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K46"/>
+      <x:c r="L46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="78" t="str">
@@ -4389,6 +4753,10 @@
       <x:c r="J47" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K47"/>
+      <x:c r="L47" t="str">
+        <x:v>https://www.youtube.com/watch?v=50KX3DZxw60</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="78" t="str">
@@ -4415,6 +4783,8 @@
       <x:c r="J48" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K48"/>
+      <x:c r="L48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="78" t="str">
@@ -4441,6 +4811,8 @@
       <x:c r="J49" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K49"/>
+      <x:c r="L49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="78" t="str">
@@ -4467,6 +4839,8 @@
       <x:c r="J50" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K50"/>
+      <x:c r="L50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="78" t="str">
@@ -4493,6 +4867,8 @@
       <x:c r="J51" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K51"/>
+      <x:c r="L51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="78" t="str">
@@ -4519,6 +4895,8 @@
       <x:c r="J52" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K52"/>
+      <x:c r="L52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="78" t="str">
@@ -4545,6 +4923,8 @@
       <x:c r="J53" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K53"/>
+      <x:c r="L53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="78" t="str">
@@ -4571,6 +4951,8 @@
       <x:c r="J54" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K54"/>
+      <x:c r="L54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="78" t="str">
@@ -4597,6 +4979,8 @@
       <x:c r="J55" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K55"/>
+      <x:c r="L55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="78" t="str">
@@ -4623,6 +5007,8 @@
       <x:c r="J56" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K56"/>
+      <x:c r="L56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="74" t="str">
@@ -4649,6 +5035,8 @@
       <x:c r="J57" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K57"/>
+      <x:c r="L57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="74" t="str">
@@ -4675,6 +5063,8 @@
       <x:c r="J58" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K58"/>
+      <x:c r="L58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="74" t="str">
@@ -4701,6 +5091,8 @@
       <x:c r="J59" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K59"/>
+      <x:c r="L59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="74" t="str">
@@ -4727,6 +5119,8 @@
       <x:c r="J60" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K60"/>
+      <x:c r="L60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="79" t="str">
@@ -4753,6 +5147,8 @@
       <x:c r="J61" s="79" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K61"/>
+      <x:c r="L61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="79"/>
@@ -4765,6 +5161,8 @@
       <x:c r="H62" s="79"/>
       <x:c r="I62" s="79"/>
       <x:c r="J62" s="79"/>
+      <x:c r="K62"/>
+      <x:c r="L62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="80" t="str">
@@ -4791,6 +5189,8 @@
       <x:c r="J63" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K63"/>
+      <x:c r="L63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="80" t="str">
@@ -4817,6 +5217,8 @@
       <x:c r="J64" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K64"/>
+      <x:c r="L64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="80" t="str">
@@ -4843,6 +5245,8 @@
       <x:c r="J65" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K65"/>
+      <x:c r="L65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="80" t="str">
@@ -4869,6 +5273,8 @@
       <x:c r="J66" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K66"/>
+      <x:c r="L66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="80" t="str">
@@ -4895,6 +5301,8 @@
       <x:c r="J67" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K67"/>
+      <x:c r="L67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="80" t="str">
@@ -4921,6 +5329,8 @@
       <x:c r="J68" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K68"/>
+      <x:c r="L68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="80" t="str">
@@ -4947,6 +5357,8 @@
       <x:c r="J69" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K69"/>
+      <x:c r="L69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="80" t="str">
@@ -4973,6 +5385,8 @@
       <x:c r="J70" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K70"/>
+      <x:c r="L70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="80" t="str">
@@ -4999,6 +5413,8 @@
       <x:c r="J71" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K71"/>
+      <x:c r="L71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="80" t="str">
@@ -5025,6 +5441,8 @@
       <x:c r="J72" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K72"/>
+      <x:c r="L72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="74" t="str">
@@ -5051,6 +5469,8 @@
       <x:c r="J73" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K73"/>
+      <x:c r="L73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="74" t="str">
@@ -5077,6 +5497,8 @@
       <x:c r="J74" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K74"/>
+      <x:c r="L74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="74" t="str">
@@ -5103,6 +5525,8 @@
       <x:c r="J75" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K75"/>
+      <x:c r="L75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="74" t="str">
@@ -5129,6 +5553,8 @@
       <x:c r="J76" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K76"/>
+      <x:c r="L76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="74" t="str">
@@ -5155,6 +5581,8 @@
       <x:c r="J77" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K77"/>
+      <x:c r="L77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="81" t="str">
@@ -5181,6 +5609,8 @@
       <x:c r="J78" s="81" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K78"/>
+      <x:c r="L78"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5224,6 +5654,8 @@
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="48" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -5309,6 +5741,12 @@
       <x:c r="J5" s="62" t="str">
         <x:v>Hecho</x:v>
       </x:c>
+      <x:c r="K5" s="119" t="str">
+        <x:v>Indicaciones</x:v>
+      </x:c>
+      <x:c r="L5" s="119" t="str">
+        <x:v>Vídeo (YouTube, opcional)</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="73" t="str">
@@ -5335,6 +5773,8 @@
       <x:c r="J6" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="73" t="str">
@@ -5361,6 +5801,10 @@
       <x:c r="J7" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K7"/>
+      <x:c r="L7" t="str">
+        <x:v>https://www.youtube.com/watch?v=50KX3DZxw60</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="73" t="str">
@@ -5387,6 +5831,8 @@
       <x:c r="J8" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="73" t="str">
@@ -5413,6 +5859,8 @@
       <x:c r="J9" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="73" t="str">
@@ -5439,6 +5887,8 @@
       <x:c r="J10" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="73" t="str">
@@ -5465,6 +5915,8 @@
       <x:c r="J11" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="73" t="str">
@@ -5491,6 +5943,8 @@
       <x:c r="J12" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="73" t="str">
@@ -5517,6 +5971,8 @@
       <x:c r="J13" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="73" t="str">
@@ -5543,6 +5999,8 @@
       <x:c r="J14" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="73" t="str">
@@ -5569,6 +6027,8 @@
       <x:c r="J15" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="73" t="str">
@@ -5595,6 +6055,8 @@
       <x:c r="J16" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="74" t="str">
@@ -5621,6 +6083,8 @@
       <x:c r="J17" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="74" t="str">
@@ -5647,6 +6111,8 @@
       <x:c r="J18" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="74" t="str">
@@ -5673,6 +6139,8 @@
       <x:c r="J19" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="74" t="str">
@@ -5699,6 +6167,8 @@
       <x:c r="J20" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="76" t="str">
@@ -5725,6 +6195,8 @@
       <x:c r="J21" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="76" t="str">
@@ -5751,6 +6223,8 @@
       <x:c r="J22" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="76" t="str">
@@ -5777,6 +6251,8 @@
       <x:c r="J23" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K23"/>
+      <x:c r="L23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="76" t="str">
@@ -5803,6 +6279,8 @@
       <x:c r="J24" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K24"/>
+      <x:c r="L24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="76" t="str">
@@ -5829,6 +6307,8 @@
       <x:c r="J25" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K25"/>
+      <x:c r="L25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="76" t="str">
@@ -5855,6 +6335,8 @@
       <x:c r="J26" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K26"/>
+      <x:c r="L26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="76" t="str">
@@ -5881,6 +6363,8 @@
       <x:c r="J27" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K27"/>
+      <x:c r="L27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="76" t="str">
@@ -5907,6 +6391,8 @@
       <x:c r="J28" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K28"/>
+      <x:c r="L28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="76" t="str">
@@ -5933,6 +6419,8 @@
       <x:c r="J29" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="76" t="str">
@@ -5959,6 +6447,8 @@
       <x:c r="J30" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K30"/>
+      <x:c r="L30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="76" t="str">
@@ -5985,6 +6475,8 @@
       <x:c r="J31" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K31"/>
+      <x:c r="L31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="74" t="str">
@@ -6011,6 +6503,8 @@
       <x:c r="J32" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="74" t="str">
@@ -6037,6 +6531,8 @@
       <x:c r="J33" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K33"/>
+      <x:c r="L33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="74" t="str">
@@ -6063,6 +6559,8 @@
       <x:c r="J34" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K34"/>
+      <x:c r="L34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="74" t="str">
@@ -6089,6 +6587,8 @@
       <x:c r="J35" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K35"/>
+      <x:c r="L35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="77" t="str">
@@ -6115,6 +6615,8 @@
       <x:c r="J36" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K36"/>
+      <x:c r="L36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="77" t="str">
@@ -6141,6 +6643,8 @@
       <x:c r="J37" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K37"/>
+      <x:c r="L37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="77" t="str">
@@ -6167,6 +6671,8 @@
       <x:c r="J38" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K38"/>
+      <x:c r="L38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="77" t="str">
@@ -6193,6 +6699,8 @@
       <x:c r="J39" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K39"/>
+      <x:c r="L39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="77" t="str">
@@ -6219,6 +6727,8 @@
       <x:c r="J40" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K40"/>
+      <x:c r="L40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="77" t="str">
@@ -6245,6 +6755,8 @@
       <x:c r="J41" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K41"/>
+      <x:c r="L41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="74" t="str">
@@ -6271,6 +6783,8 @@
       <x:c r="J42" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K42"/>
+      <x:c r="L42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="74" t="str">
@@ -6297,6 +6811,8 @@
       <x:c r="J43" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K43"/>
+      <x:c r="L43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="74" t="str">
@@ -6323,6 +6839,8 @@
       <x:c r="J44" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K44"/>
+      <x:c r="L44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="74"/>
@@ -6335,6 +6853,8 @@
       <x:c r="H45" s="74"/>
       <x:c r="I45" s="74"/>
       <x:c r="J45" s="74"/>
+      <x:c r="K45"/>
+      <x:c r="L45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="78" t="str">
@@ -6361,6 +6881,8 @@
       <x:c r="J46" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K46"/>
+      <x:c r="L46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="78" t="str">
@@ -6387,6 +6909,10 @@
       <x:c r="J47" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K47"/>
+      <x:c r="L47" t="str">
+        <x:v>https://www.youtube.com/watch?v=50KX3DZxw60</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="78" t="str">
@@ -6413,6 +6939,8 @@
       <x:c r="J48" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K48"/>
+      <x:c r="L48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="78" t="str">
@@ -6439,6 +6967,8 @@
       <x:c r="J49" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K49"/>
+      <x:c r="L49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="78" t="str">
@@ -6465,6 +6995,8 @@
       <x:c r="J50" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K50"/>
+      <x:c r="L50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="78" t="str">
@@ -6491,6 +7023,8 @@
       <x:c r="J51" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K51"/>
+      <x:c r="L51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="78" t="str">
@@ -6517,6 +7051,8 @@
       <x:c r="J52" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K52"/>
+      <x:c r="L52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="78" t="str">
@@ -6543,6 +7079,8 @@
       <x:c r="J53" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K53"/>
+      <x:c r="L53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="78" t="str">
@@ -6569,6 +7107,8 @@
       <x:c r="J54" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K54"/>
+      <x:c r="L54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="78" t="str">
@@ -6595,6 +7135,8 @@
       <x:c r="J55" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K55"/>
+      <x:c r="L55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="78" t="str">
@@ -6621,6 +7163,8 @@
       <x:c r="J56" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K56"/>
+      <x:c r="L56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="74" t="str">
@@ -6647,6 +7191,8 @@
       <x:c r="J57" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K57"/>
+      <x:c r="L57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="74" t="str">
@@ -6673,6 +7219,8 @@
       <x:c r="J58" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K58"/>
+      <x:c r="L58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="74" t="str">
@@ -6699,6 +7247,8 @@
       <x:c r="J59" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K59"/>
+      <x:c r="L59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="74" t="str">
@@ -6725,6 +7275,8 @@
       <x:c r="J60" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K60"/>
+      <x:c r="L60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="79" t="str">
@@ -6751,6 +7303,8 @@
       <x:c r="J61" s="79" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K61"/>
+      <x:c r="L61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="79"/>
@@ -6763,6 +7317,8 @@
       <x:c r="H62" s="79"/>
       <x:c r="I62" s="79"/>
       <x:c r="J62" s="79"/>
+      <x:c r="K62"/>
+      <x:c r="L62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="80" t="str">
@@ -6789,6 +7345,8 @@
       <x:c r="J63" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K63"/>
+      <x:c r="L63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="80" t="str">
@@ -6815,6 +7373,8 @@
       <x:c r="J64" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K64"/>
+      <x:c r="L64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="80" t="str">
@@ -6841,6 +7401,8 @@
       <x:c r="J65" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K65"/>
+      <x:c r="L65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="80" t="str">
@@ -6867,6 +7429,8 @@
       <x:c r="J66" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K66"/>
+      <x:c r="L66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="80" t="str">
@@ -6893,6 +7457,8 @@
       <x:c r="J67" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K67"/>
+      <x:c r="L67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="80" t="str">
@@ -6919,6 +7485,8 @@
       <x:c r="J68" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K68"/>
+      <x:c r="L68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="80" t="str">
@@ -6945,6 +7513,8 @@
       <x:c r="J69" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K69"/>
+      <x:c r="L69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="80" t="str">
@@ -6971,6 +7541,8 @@
       <x:c r="J70" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K70"/>
+      <x:c r="L70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="80" t="str">
@@ -6997,6 +7569,8 @@
       <x:c r="J71" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K71"/>
+      <x:c r="L71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="80" t="str">
@@ -7023,6 +7597,8 @@
       <x:c r="J72" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K72"/>
+      <x:c r="L72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="74" t="str">
@@ -7049,6 +7625,8 @@
       <x:c r="J73" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K73"/>
+      <x:c r="L73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="74" t="str">
@@ -7075,6 +7653,8 @@
       <x:c r="J74" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K74"/>
+      <x:c r="L74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="74" t="str">
@@ -7101,6 +7681,8 @@
       <x:c r="J75" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K75"/>
+      <x:c r="L75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="74" t="str">
@@ -7127,6 +7709,8 @@
       <x:c r="J76" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K76"/>
+      <x:c r="L76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="74" t="str">
@@ -7153,6 +7737,8 @@
       <x:c r="J77" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K77"/>
+      <x:c r="L77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="81" t="str">
@@ -7179,6 +7765,8 @@
       <x:c r="J78" s="81" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K78"/>
+      <x:c r="L78"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7222,6 +7810,8 @@
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="48" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -7307,6 +7897,12 @@
       <x:c r="J5" s="62" t="str">
         <x:v>Hecho</x:v>
       </x:c>
+      <x:c r="K5" s="119" t="str">
+        <x:v>Indicaciones</x:v>
+      </x:c>
+      <x:c r="L5" s="119" t="str">
+        <x:v>Vídeo (YouTube, opcional)</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="73" t="str">
@@ -7333,6 +7929,8 @@
       <x:c r="J6" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="73" t="str">
@@ -7359,6 +7957,10 @@
       <x:c r="J7" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K7"/>
+      <x:c r="L7" t="str">
+        <x:v>https://www.youtube.com/watch?v=50KX3DZxw60</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="73" t="str">
@@ -7385,6 +7987,8 @@
       <x:c r="J8" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="73" t="str">
@@ -7411,6 +8015,8 @@
       <x:c r="J9" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="73" t="str">
@@ -7437,6 +8043,8 @@
       <x:c r="J10" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="73" t="str">
@@ -7463,6 +8071,8 @@
       <x:c r="J11" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="73" t="str">
@@ -7489,6 +8099,8 @@
       <x:c r="J12" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="73" t="str">
@@ -7515,6 +8127,8 @@
       <x:c r="J13" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="73" t="str">
@@ -7541,6 +8155,8 @@
       <x:c r="J14" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="73" t="str">
@@ -7567,6 +8183,8 @@
       <x:c r="J15" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="73" t="str">
@@ -7593,6 +8211,8 @@
       <x:c r="J16" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="74" t="str">
@@ -7619,6 +8239,8 @@
       <x:c r="J17" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="74" t="str">
@@ -7645,6 +8267,8 @@
       <x:c r="J18" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="74" t="str">
@@ -7671,6 +8295,8 @@
       <x:c r="J19" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="74" t="str">
@@ -7697,6 +8323,8 @@
       <x:c r="J20" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="76" t="str">
@@ -7723,6 +8351,8 @@
       <x:c r="J21" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="76" t="str">
@@ -7749,6 +8379,8 @@
       <x:c r="J22" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="76" t="str">
@@ -7775,6 +8407,8 @@
       <x:c r="J23" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K23"/>
+      <x:c r="L23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="76" t="str">
@@ -7801,6 +8435,8 @@
       <x:c r="J24" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K24"/>
+      <x:c r="L24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="76" t="str">
@@ -7827,6 +8463,8 @@
       <x:c r="J25" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K25"/>
+      <x:c r="L25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="76" t="str">
@@ -7853,6 +8491,8 @@
       <x:c r="J26" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K26"/>
+      <x:c r="L26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="76" t="str">
@@ -7879,6 +8519,8 @@
       <x:c r="J27" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K27"/>
+      <x:c r="L27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="76" t="str">
@@ -7905,6 +8547,8 @@
       <x:c r="J28" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K28"/>
+      <x:c r="L28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="76" t="str">
@@ -7931,6 +8575,8 @@
       <x:c r="J29" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="76" t="str">
@@ -7957,6 +8603,8 @@
       <x:c r="J30" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K30"/>
+      <x:c r="L30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="76" t="str">
@@ -7983,6 +8631,8 @@
       <x:c r="J31" s="76" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K31"/>
+      <x:c r="L31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="74" t="str">
@@ -8009,6 +8659,8 @@
       <x:c r="J32" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="74" t="str">
@@ -8035,6 +8687,8 @@
       <x:c r="J33" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K33"/>
+      <x:c r="L33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="74" t="str">
@@ -8061,6 +8715,8 @@
       <x:c r="J34" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K34"/>
+      <x:c r="L34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="74" t="str">
@@ -8087,6 +8743,8 @@
       <x:c r="J35" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K35"/>
+      <x:c r="L35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="77" t="str">
@@ -8113,6 +8771,8 @@
       <x:c r="J36" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K36"/>
+      <x:c r="L36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="77" t="str">
@@ -8139,6 +8799,8 @@
       <x:c r="J37" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K37"/>
+      <x:c r="L37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="77" t="str">
@@ -8165,6 +8827,8 @@
       <x:c r="J38" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K38"/>
+      <x:c r="L38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="77" t="str">
@@ -8191,6 +8855,8 @@
       <x:c r="J39" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K39"/>
+      <x:c r="L39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="77" t="str">
@@ -8217,6 +8883,8 @@
       <x:c r="J40" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K40"/>
+      <x:c r="L40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="77" t="str">
@@ -8243,6 +8911,8 @@
       <x:c r="J41" s="77" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K41"/>
+      <x:c r="L41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="74" t="str">
@@ -8269,6 +8939,8 @@
       <x:c r="J42" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K42"/>
+      <x:c r="L42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="74" t="str">
@@ -8295,6 +8967,8 @@
       <x:c r="J43" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K43"/>
+      <x:c r="L43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="74" t="str">
@@ -8321,6 +8995,8 @@
       <x:c r="J44" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K44"/>
+      <x:c r="L44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="74"/>
@@ -8333,6 +9009,8 @@
       <x:c r="H45" s="74"/>
       <x:c r="I45" s="74"/>
       <x:c r="J45" s="74"/>
+      <x:c r="K45"/>
+      <x:c r="L45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="78" t="str">
@@ -8359,6 +9037,8 @@
       <x:c r="J46" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K46"/>
+      <x:c r="L46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="78" t="str">
@@ -8385,6 +9065,10 @@
       <x:c r="J47" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K47"/>
+      <x:c r="L47" t="str">
+        <x:v>https://www.youtube.com/watch?v=50KX3DZxw60</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="78" t="str">
@@ -8411,6 +9095,8 @@
       <x:c r="J48" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K48"/>
+      <x:c r="L48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="78" t="str">
@@ -8437,6 +9123,8 @@
       <x:c r="J49" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K49"/>
+      <x:c r="L49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="78" t="str">
@@ -8463,6 +9151,8 @@
       <x:c r="J50" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K50"/>
+      <x:c r="L50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="78" t="str">
@@ -8489,6 +9179,8 @@
       <x:c r="J51" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K51"/>
+      <x:c r="L51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="78" t="str">
@@ -8515,6 +9207,8 @@
       <x:c r="J52" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K52"/>
+      <x:c r="L52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="78" t="str">
@@ -8541,6 +9235,8 @@
       <x:c r="J53" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K53"/>
+      <x:c r="L53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="78" t="str">
@@ -8567,6 +9263,8 @@
       <x:c r="J54" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K54"/>
+      <x:c r="L54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="78" t="str">
@@ -8593,6 +9291,8 @@
       <x:c r="J55" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K55"/>
+      <x:c r="L55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="78" t="str">
@@ -8619,6 +9319,8 @@
       <x:c r="J56" s="78" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K56"/>
+      <x:c r="L56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="74" t="str">
@@ -8645,6 +9347,8 @@
       <x:c r="J57" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K57"/>
+      <x:c r="L57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="74" t="str">
@@ -8671,6 +9375,8 @@
       <x:c r="J58" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K58"/>
+      <x:c r="L58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="74" t="str">
@@ -8697,6 +9403,8 @@
       <x:c r="J59" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K59"/>
+      <x:c r="L59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="74" t="str">
@@ -8723,6 +9431,8 @@
       <x:c r="J60" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K60"/>
+      <x:c r="L60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="79" t="str">
@@ -8749,6 +9459,8 @@
       <x:c r="J61" s="79" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K61"/>
+      <x:c r="L61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="79"/>
@@ -8761,6 +9473,8 @@
       <x:c r="H62" s="79"/>
       <x:c r="I62" s="79"/>
       <x:c r="J62" s="79"/>
+      <x:c r="K62"/>
+      <x:c r="L62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="80" t="str">
@@ -8787,6 +9501,8 @@
       <x:c r="J63" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K63"/>
+      <x:c r="L63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="80" t="str">
@@ -8813,6 +9529,8 @@
       <x:c r="J64" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K64"/>
+      <x:c r="L64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="80" t="str">
@@ -8839,6 +9557,8 @@
       <x:c r="J65" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K65"/>
+      <x:c r="L65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="80" t="str">
@@ -8865,6 +9585,8 @@
       <x:c r="J66" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K66"/>
+      <x:c r="L66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="80" t="str">
@@ -8891,6 +9613,8 @@
       <x:c r="J67" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K67"/>
+      <x:c r="L67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="80" t="str">
@@ -8917,6 +9641,8 @@
       <x:c r="J68" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K68"/>
+      <x:c r="L68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="80" t="str">
@@ -8943,6 +9669,8 @@
       <x:c r="J69" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K69"/>
+      <x:c r="L69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="80" t="str">
@@ -8969,6 +9697,8 @@
       <x:c r="J70" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K70"/>
+      <x:c r="L70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="80" t="str">
@@ -8995,6 +9725,8 @@
       <x:c r="J71" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K71"/>
+      <x:c r="L71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="80" t="str">
@@ -9021,6 +9753,8 @@
       <x:c r="J72" s="80" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K72"/>
+      <x:c r="L72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="74" t="str">
@@ -9047,6 +9781,8 @@
       <x:c r="J73" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K73"/>
+      <x:c r="L73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="74" t="str">
@@ -9073,6 +9809,8 @@
       <x:c r="J74" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K74"/>
+      <x:c r="L74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="74" t="str">
@@ -9099,6 +9837,8 @@
       <x:c r="J75" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K75"/>
+      <x:c r="L75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="74" t="str">
@@ -9125,6 +9865,8 @@
       <x:c r="J76" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K76"/>
+      <x:c r="L76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="74" t="str">
@@ -9151,6 +9893,8 @@
       <x:c r="J77" s="74" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K77"/>
+      <x:c r="L77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="81" t="str">
@@ -9177,6 +9921,8 @@
       <x:c r="J78" s="81" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="K78"/>
+      <x:c r="L78"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9376,6 +10122,7 @@
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -9433,6 +10180,9 @@
       <x:c r="F5" s="99" t="str">
         <x:v>Indicaciones</x:v>
       </x:c>
+      <x:c r="G5" s="119" t="str">
+        <x:v>Vídeo (YouTube, opcional)</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="102" t="n">
@@ -9453,6 +10203,7 @@
       <x:c r="F6" s="100" t="str">
         <x:v>Ritmo cómodo; debes poder mantener una conversación.</x:v>
       </x:c>
+      <x:c r="G6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="102" t="n">
@@ -9473,6 +10224,7 @@
       <x:c r="F7" s="100" t="str">
         <x:v>Talón apoyado; lleva la rodilla hacia la pared sin forzar.</x:v>
       </x:c>
+      <x:c r="G7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="102" t="n">
@@ -9493,6 +10245,7 @@
       <x:c r="F8" s="100" t="str">
         <x:v>Movimiento lento y controlado.</x:v>
       </x:c>
+      <x:c r="G8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="102" t="n">
@@ -9513,6 +10266,7 @@
       <x:c r="F9" s="100" t="str">
         <x:v>Aprieta ligeramente el glúteo de la pierna atrasada.</x:v>
       </x:c>
+      <x:c r="G9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="102" t="n">
@@ -9533,6 +10287,7 @@
       <x:c r="F10" s="100" t="str">
         <x:v>Gira desde la parte alta de la espalda, sin forzar lumbar.</x:v>
       </x:c>
+      <x:c r="G10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="102" t="n">
@@ -9553,6 +10308,7 @@
       <x:c r="F11" s="100" t="str">
         <x:v>Amplios pero cómodos.</x:v>
       </x:c>
+      <x:c r="G11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="102" t="n">
@@ -9573,6 +10329,7 @@
       <x:c r="F12" s="100" t="str">
         <x:v>Suave; hombro lejos de la oreja.</x:v>
       </x:c>
+      <x:c r="G12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="102" t="n">
@@ -9593,6 +10350,7 @@
       <x:c r="F13" s="100" t="str">
         <x:v>Sin peso, rango cómodo.</x:v>
       </x:c>
+      <x:c r="G13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="102" t="n">
@@ -9613,6 +10371,7 @@
       <x:c r="F14" s="100" t="str">
         <x:v>Sin peso; codo pegado al cuerpo.</x:v>
       </x:c>
+      <x:c r="G14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="103" t="n">
@@ -9633,6 +10392,7 @@
       <x:c r="F15" s="101" t="str">
         <x:v>Inhala por nariz y exhala lentamente.</x:v>
       </x:c>
+      <x:c r="G15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="70"/>
@@ -9694,6 +10454,7 @@
     <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="80" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -9738,6 +10499,9 @@
       <x:c r="D4" s="111" t="str">
         <x:v>Indicaciones</x:v>
       </x:c>
+      <x:c r="E4" s="122" t="str">
+        <x:v>Vídeo (YouTube, opcional)</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="114" t="n">
@@ -9752,6 +10516,7 @@
       <x:c r="D5" s="114" t="str">
         <x:v>Camina en el sitio y acompaña el movimiento con los brazos. Empieza despacio y aumenta el ritmo poco a poco.</x:v>
       </x:c>
+      <x:c r="E5"/>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="114" t="n">
@@ -9766,6 +10531,7 @@
       <x:c r="D6" s="114" t="str">
         <x:v>Haz círculos suaves con los hombros. Después, abre y cierra los brazos sin forzar las articulaciones.</x:v>
       </x:c>
+      <x:c r="E6"/>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="114" t="n">
@@ -9780,6 +10546,7 @@
       <x:c r="D7" s="114" t="str">
         <x:v>Gira el tronco lentamente a cada lado y alterna inclinaciones laterales. Mantén la respiración tranquila.</x:v>
       </x:c>
+      <x:c r="E7"/>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="114" t="n">
@@ -9794,6 +10561,7 @@
       <x:c r="D8" s="114" t="str">
         <x:v>Eleva una rodilla cada vez, dibuja círculos pequeños con la cadera y mueve los tobillos apoyándote si lo necesitas.</x:v>
       </x:c>
+      <x:c r="E8"/>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="114" t="n">
@@ -9808,6 +10576,7 @@
       <x:c r="D9" s="114" t="str">
         <x:v>Alterna pasos laterales, elevaciones de talones y flexiones de rodilla poco profundas, a un ritmo cómodo.</x:v>
       </x:c>
+      <x:c r="E9"/>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
       <x:c r="A10" s="114" t="n">
@@ -9822,6 +10591,7 @@
       <x:c r="D10" s="114" t="str">
         <x:v>Termina con gemelos, costados y brazos. Mantén cada posición unos segundos, sin rebotes ni dolor.</x:v>
       </x:c>
+      <x:c r="E10"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
